--- a/artfynd/A 57726-2021 artfynd.xlsx
+++ b/artfynd/A 57726-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121325384</v>
+        <v>121325391</v>
       </c>
       <c r="B2" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vemasmägg, Vemasmägg, Dlr</t>
+          <t>Blocktjärnen, Blocktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483864</v>
+        <v>483983</v>
       </c>
       <c r="R2" t="n">
-        <v>6836259</v>
+        <v>6836105</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,6 +753,11 @@
           <t>2024-11-24</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På tall</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -765,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121325391</v>
+        <v>121325458</v>
       </c>
       <c r="B3" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,14 +818,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Blocktjärnen, Blocktjärnen, Dlr</t>
+          <t>Vemasmägg, Vemasmägg, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483983</v>
+        <v>483838</v>
       </c>
       <c r="R3" t="n">
-        <v>6836105</v>
+        <v>6836236</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,11 +860,6 @@
           <t>2024-11-24</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På tall</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -872,12 +872,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -887,7 +887,7 @@
         <v>121325415</v>
       </c>
       <c r="B4" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121326083</v>
+        <v>121325384</v>
       </c>
       <c r="B5" t="n">
-        <v>78335</v>
+        <v>78601</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,37 +1002,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Blocktjärnen, Blocktjärnen, Dlr</t>
+          <t>Vemasmägg, Vemasmägg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483983</v>
+        <v>483864</v>
       </c>
       <c r="R5" t="n">
-        <v>6836105</v>
+        <v>6836259</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1076,22 +1076,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121325458</v>
+        <v>121326083</v>
       </c>
       <c r="B6" t="n">
-        <v>78598</v>
+        <v>78338</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,37 +1104,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vemasmägg, Vemasmägg, Dlr</t>
+          <t>Blocktjärnen, Blocktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483838</v>
+        <v>483983</v>
       </c>
       <c r="R6" t="n">
-        <v>6836236</v>
+        <v>6836105</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,12 +1178,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 57726-2021 artfynd.xlsx
+++ b/artfynd/A 57726-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121325391</v>
+        <v>121325384</v>
       </c>
       <c r="B2" t="n">
         <v>78601</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Blocktjärnen, Blocktjärnen, Dlr</t>
+          <t>Vemasmägg, Vemasmägg, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483983</v>
+        <v>483864</v>
       </c>
       <c r="R2" t="n">
-        <v>6836105</v>
+        <v>6836259</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,11 +753,6 @@
           <t>2024-11-24</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På tall</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -770,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121325458</v>
+        <v>121326083</v>
       </c>
       <c r="B3" t="n">
-        <v>78601</v>
+        <v>78338</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vemasmägg, Vemasmägg, Dlr</t>
+          <t>Blocktjärnen, Blocktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483838</v>
+        <v>483983</v>
       </c>
       <c r="R3" t="n">
-        <v>6836236</v>
+        <v>6836105</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,19 +867,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121325415</v>
+        <v>121325391</v>
       </c>
       <c r="B4" t="n">
         <v>78601</v>
@@ -927,7 +922,7 @@
         <v>483983</v>
       </c>
       <c r="R4" t="n">
-        <v>6836063</v>
+        <v>6836105</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-24</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121325384</v>
+        <v>121325458</v>
       </c>
       <c r="B5" t="n">
         <v>78601</v>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483864</v>
+        <v>483838</v>
       </c>
       <c r="R5" t="n">
-        <v>6836259</v>
+        <v>6836236</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121326083</v>
+        <v>121325415</v>
       </c>
       <c r="B6" t="n">
-        <v>78338</v>
+        <v>78601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1131,10 +1131,10 @@
         <v>483983</v>
       </c>
       <c r="R6" t="n">
-        <v>6836105</v>
+        <v>6836063</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 57726-2021 artfynd.xlsx
+++ b/artfynd/A 57726-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121325384</v>
+        <v>121325458</v>
       </c>
       <c r="B2" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483864</v>
+        <v>483838</v>
       </c>
       <c r="R2" t="n">
-        <v>6836259</v>
+        <v>6836236</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121326083</v>
+        <v>121325391</v>
       </c>
       <c r="B3" t="n">
-        <v>78338</v>
+        <v>78604</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -823,7 +823,7 @@
         <v>6836105</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-24</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121325391</v>
+        <v>121326083</v>
       </c>
       <c r="B4" t="n">
-        <v>78601</v>
+        <v>78341</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -925,7 +930,7 @@
         <v>6836105</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -955,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-24</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121325458</v>
+        <v>121325415</v>
       </c>
       <c r="B5" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,14 +1022,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vemasmägg, Vemasmägg, Dlr</t>
+          <t>Blocktjärnen, Blocktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483838</v>
+        <v>483983</v>
       </c>
       <c r="R5" t="n">
-        <v>6836236</v>
+        <v>6836063</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,22 +1076,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121325415</v>
+        <v>121325384</v>
       </c>
       <c r="B6" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,14 +1124,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Blocktjärnen, Blocktjärnen, Dlr</t>
+          <t>Vemasmägg, Vemasmägg, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483983</v>
+        <v>483864</v>
       </c>
       <c r="R6" t="n">
-        <v>6836063</v>
+        <v>6836259</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,12 +1178,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 57726-2021 artfynd.xlsx
+++ b/artfynd/A 57726-2021 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121325391</v>
+        <v>121325384</v>
       </c>
       <c r="B3" t="n">
         <v>78604</v>
@@ -813,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Blocktjärnen, Blocktjärnen, Dlr</t>
+          <t>Vemasmägg, Vemasmägg, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483983</v>
+        <v>483864</v>
       </c>
       <c r="R3" t="n">
-        <v>6836105</v>
+        <v>6836259</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,11 +855,6 @@
           <t>2024-11-24</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På tall</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -872,12 +867,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -986,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121325415</v>
+        <v>121325391</v>
       </c>
       <c r="B5" t="n">
         <v>78604</v>
@@ -1029,7 +1024,7 @@
         <v>483983</v>
       </c>
       <c r="R5" t="n">
-        <v>6836063</v>
+        <v>6836105</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-24</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121325384</v>
+        <v>121325415</v>
       </c>
       <c r="B6" t="n">
         <v>78604</v>
@@ -1124,14 +1124,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vemasmägg, Vemasmägg, Dlr</t>
+          <t>Blocktjärnen, Blocktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483864</v>
+        <v>483983</v>
       </c>
       <c r="R6" t="n">
-        <v>6836259</v>
+        <v>6836063</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,12 +1178,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 57726-2021 artfynd.xlsx
+++ b/artfynd/A 57726-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121325458</v>
+        <v>121325415</v>
       </c>
       <c r="B2" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vemasmägg, Vemasmägg, Dlr</t>
+          <t>Blocktjärnen, Blocktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483838</v>
+        <v>483983</v>
       </c>
       <c r="R2" t="n">
-        <v>6836236</v>
+        <v>6836063</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121325384</v>
+        <v>121325391</v>
       </c>
       <c r="B3" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vemasmägg, Vemasmägg, Dlr</t>
+          <t>Blocktjärnen, Blocktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483864</v>
+        <v>483983</v>
       </c>
       <c r="R3" t="n">
-        <v>6836259</v>
+        <v>6836105</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,6 +855,11 @@
           <t>2024-11-24</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På tall</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -867,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121326083</v>
+        <v>121325384</v>
       </c>
       <c r="B4" t="n">
-        <v>78341</v>
+        <v>78607</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,37 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Blocktjärnen, Blocktjärnen, Dlr</t>
+          <t>Vemasmägg, Vemasmägg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483983</v>
+        <v>483864</v>
       </c>
       <c r="R4" t="n">
-        <v>6836105</v>
+        <v>6836259</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +974,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121325391</v>
+        <v>121326083</v>
       </c>
       <c r="B5" t="n">
-        <v>78604</v>
+        <v>78344</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1027,7 +1032,7 @@
         <v>6836105</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1057,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-24</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121325415</v>
+        <v>121325458</v>
       </c>
       <c r="B6" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,14 +1124,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Blocktjärnen, Blocktjärnen, Dlr</t>
+          <t>Vemasmägg, Vemasmägg, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483983</v>
+        <v>483838</v>
       </c>
       <c r="R6" t="n">
-        <v>6836063</v>
+        <v>6836236</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,12 +1178,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 57726-2021 artfynd.xlsx
+++ b/artfynd/A 57726-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121325415</v>
+        <v>121325391</v>
       </c>
       <c r="B2" t="n">
         <v>78607</v>
@@ -718,7 +718,7 @@
         <v>483983</v>
       </c>
       <c r="R2" t="n">
-        <v>6836063</v>
+        <v>6836105</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-24</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121325391</v>
+        <v>121325458</v>
       </c>
       <c r="B3" t="n">
         <v>78607</v>
@@ -813,14 +818,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Blocktjärnen, Blocktjärnen, Dlr</t>
+          <t>Vemasmägg, Vemasmägg, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483983</v>
+        <v>483838</v>
       </c>
       <c r="R3" t="n">
-        <v>6836105</v>
+        <v>6836236</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,11 +860,6 @@
           <t>2024-11-24</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På tall</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -872,12 +872,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121326083</v>
+        <v>121325415</v>
       </c>
       <c r="B5" t="n">
-        <v>78344</v>
+        <v>78607</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1029,10 @@
         <v>483983</v>
       </c>
       <c r="R5" t="n">
-        <v>6836105</v>
+        <v>6836063</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121325458</v>
+        <v>121326083</v>
       </c>
       <c r="B6" t="n">
-        <v>78607</v>
+        <v>78344</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,37 +1104,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vemasmägg, Vemasmägg, Dlr</t>
+          <t>Blocktjärnen, Blocktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483838</v>
+        <v>483983</v>
       </c>
       <c r="R6" t="n">
-        <v>6836236</v>
+        <v>6836105</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,12 +1178,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 57726-2021 artfynd.xlsx
+++ b/artfynd/A 57726-2021 artfynd.xlsx
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121325384</v>
+        <v>121326083</v>
       </c>
       <c r="B4" t="n">
-        <v>78607</v>
+        <v>78344</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,37 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vemasmägg, Vemasmägg, Dlr</t>
+          <t>Blocktjärnen, Blocktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483864</v>
+        <v>483983</v>
       </c>
       <c r="R4" t="n">
-        <v>6836259</v>
+        <v>6836105</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,19 +974,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121325415</v>
+        <v>121325384</v>
       </c>
       <c r="B5" t="n">
         <v>78607</v>
@@ -1022,14 +1022,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Blocktjärnen, Blocktjärnen, Dlr</t>
+          <t>Vemasmägg, Vemasmägg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483983</v>
+        <v>483864</v>
       </c>
       <c r="R5" t="n">
-        <v>6836063</v>
+        <v>6836259</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,22 +1076,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121326083</v>
+        <v>121325415</v>
       </c>
       <c r="B6" t="n">
-        <v>78344</v>
+        <v>78607</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1131,10 +1131,10 @@
         <v>483983</v>
       </c>
       <c r="R6" t="n">
-        <v>6836105</v>
+        <v>6836063</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 57726-2021 artfynd.xlsx
+++ b/artfynd/A 57726-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121325391</v>
+        <v>121325384</v>
       </c>
       <c r="B2" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Blocktjärnen, Blocktjärnen, Dlr</t>
+          <t>Vemasmägg, Vemasmägg, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483983</v>
+        <v>483864</v>
       </c>
       <c r="R2" t="n">
-        <v>6836105</v>
+        <v>6836259</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,11 +753,6 @@
           <t>2024-11-24</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På tall</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -770,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121325458</v>
+        <v>121325391</v>
       </c>
       <c r="B3" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vemasmägg, Vemasmägg, Dlr</t>
+          <t>Blocktjärnen, Blocktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483838</v>
+        <v>483983</v>
       </c>
       <c r="R3" t="n">
-        <v>6836236</v>
+        <v>6836105</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,6 +855,11 @@
           <t>2024-11-24</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På tall</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -872,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121326083</v>
+        <v>121325458</v>
       </c>
       <c r="B4" t="n">
-        <v>78344</v>
+        <v>78608</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,37 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Blocktjärnen, Blocktjärnen, Dlr</t>
+          <t>Vemasmägg, Vemasmägg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483983</v>
+        <v>483838</v>
       </c>
       <c r="R4" t="n">
-        <v>6836105</v>
+        <v>6836236</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,22 +974,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121325384</v>
+        <v>121325415</v>
       </c>
       <c r="B5" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,14 +1022,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vemasmägg, Vemasmägg, Dlr</t>
+          <t>Blocktjärnen, Blocktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483864</v>
+        <v>483983</v>
       </c>
       <c r="R5" t="n">
-        <v>6836259</v>
+        <v>6836063</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,22 +1076,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121325415</v>
+        <v>121326083</v>
       </c>
       <c r="B6" t="n">
-        <v>78607</v>
+        <v>78345</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1131,10 +1131,10 @@
         <v>483983</v>
       </c>
       <c r="R6" t="n">
-        <v>6836063</v>
+        <v>6836105</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 57726-2021 artfynd.xlsx
+++ b/artfynd/A 57726-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121325384</v>
+        <v>121325415</v>
       </c>
       <c r="B2" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vemasmägg, Vemasmägg, Dlr</t>
+          <t>Blocktjärnen, Blocktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483864</v>
+        <v>483983</v>
       </c>
       <c r="R2" t="n">
-        <v>6836259</v>
+        <v>6836063</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121325391</v>
+        <v>121325384</v>
       </c>
       <c r="B3" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Blocktjärnen, Blocktjärnen, Dlr</t>
+          <t>Vemasmägg, Vemasmägg, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483983</v>
+        <v>483864</v>
       </c>
       <c r="R3" t="n">
-        <v>6836105</v>
+        <v>6836259</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,11 +855,6 @@
           <t>2024-11-24</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På tall</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -872,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121325458</v>
+        <v>121325391</v>
       </c>
       <c r="B4" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,14 +915,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vemasmägg, Vemasmägg, Dlr</t>
+          <t>Blocktjärnen, Blocktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483838</v>
+        <v>483983</v>
       </c>
       <c r="R4" t="n">
-        <v>6836236</v>
+        <v>6836105</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,6 +957,11 @@
           <t>2024-11-24</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På tall</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -974,22 +974,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121325415</v>
+        <v>121325458</v>
       </c>
       <c r="B5" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,14 +1022,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Blocktjärnen, Blocktjärnen, Dlr</t>
+          <t>Vemasmägg, Vemasmägg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483983</v>
+        <v>483838</v>
       </c>
       <c r="R5" t="n">
-        <v>6836063</v>
+        <v>6836236</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,12 +1076,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1091,7 +1091,7 @@
         <v>121326083</v>
       </c>
       <c r="B6" t="n">
-        <v>78345</v>
+        <v>78346</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 57726-2021 artfynd.xlsx
+++ b/artfynd/A 57726-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121325415</v>
+        <v>121325458</v>
       </c>
       <c r="B2" t="n">
         <v>78609</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Blocktjärnen, Blocktjärnen, Dlr</t>
+          <t>Vemasmägg, Vemasmägg, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483983</v>
+        <v>483838</v>
       </c>
       <c r="R2" t="n">
-        <v>6836063</v>
+        <v>6836236</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121325384</v>
+        <v>121326083</v>
       </c>
       <c r="B3" t="n">
-        <v>78609</v>
+        <v>78346</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vemasmägg, Vemasmägg, Dlr</t>
+          <t>Blocktjärnen, Blocktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483864</v>
+        <v>483983</v>
       </c>
       <c r="R3" t="n">
-        <v>6836259</v>
+        <v>6836105</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,19 +867,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121325391</v>
+        <v>121325415</v>
       </c>
       <c r="B4" t="n">
         <v>78609</v>
@@ -922,7 +922,7 @@
         <v>483983</v>
       </c>
       <c r="R4" t="n">
-        <v>6836105</v>
+        <v>6836063</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +955,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-24</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121325458</v>
+        <v>121325384</v>
       </c>
       <c r="B5" t="n">
         <v>78609</v>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483838</v>
+        <v>483864</v>
       </c>
       <c r="R5" t="n">
-        <v>6836236</v>
+        <v>6836259</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121326083</v>
+        <v>121325391</v>
       </c>
       <c r="B6" t="n">
-        <v>78346</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1134,7 +1129,7 @@
         <v>6836105</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1164,6 +1159,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-24</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 57726-2021 artfynd.xlsx
+++ b/artfynd/A 57726-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121325458</v>
+        <v>121325384</v>
       </c>
       <c r="B2" t="n">
         <v>78609</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483838</v>
+        <v>483864</v>
       </c>
       <c r="R2" t="n">
-        <v>6836236</v>
+        <v>6836259</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121326083</v>
+        <v>121325391</v>
       </c>
       <c r="B3" t="n">
-        <v>78346</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -823,7 +823,7 @@
         <v>6836105</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-24</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121325415</v>
+        <v>121325458</v>
       </c>
       <c r="B4" t="n">
         <v>78609</v>
@@ -915,14 +920,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Blocktjärnen, Blocktjärnen, Dlr</t>
+          <t>Vemasmägg, Vemasmägg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483983</v>
+        <v>483838</v>
       </c>
       <c r="R4" t="n">
-        <v>6836063</v>
+        <v>6836236</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,22 +974,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121325384</v>
+        <v>121326083</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>78346</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,37 +1002,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vemasmägg, Vemasmägg, Dlr</t>
+          <t>Blocktjärnen, Blocktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483864</v>
+        <v>483983</v>
       </c>
       <c r="R5" t="n">
-        <v>6836259</v>
+        <v>6836105</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,19 +1076,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121325391</v>
+        <v>121325415</v>
       </c>
       <c r="B6" t="n">
         <v>78609</v>
@@ -1126,7 +1131,7 @@
         <v>483983</v>
       </c>
       <c r="R6" t="n">
-        <v>6836105</v>
+        <v>6836063</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1159,11 +1164,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-24</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 57726-2021 artfynd.xlsx
+++ b/artfynd/A 57726-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121325384</v>
+        <v>121325458</v>
       </c>
       <c r="B2" t="n">
         <v>78609</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483864</v>
+        <v>483838</v>
       </c>
       <c r="R2" t="n">
-        <v>6836259</v>
+        <v>6836236</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121325458</v>
+        <v>121325384</v>
       </c>
       <c r="B4" t="n">
         <v>78609</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483838</v>
+        <v>483864</v>
       </c>
       <c r="R4" t="n">
-        <v>6836236</v>
+        <v>6836259</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121326083</v>
+        <v>121325415</v>
       </c>
       <c r="B5" t="n">
-        <v>78346</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1029,10 @@
         <v>483983</v>
       </c>
       <c r="R5" t="n">
-        <v>6836105</v>
+        <v>6836063</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121325415</v>
+        <v>121326083</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
+        <v>78346</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1131,10 +1131,10 @@
         <v>483983</v>
       </c>
       <c r="R6" t="n">
-        <v>6836063</v>
+        <v>6836105</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 57726-2021 artfynd.xlsx
+++ b/artfynd/A 57726-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121325458</v>
+        <v>121326083</v>
       </c>
       <c r="B2" t="n">
-        <v>78609</v>
+        <v>78353</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vemasmägg, Vemasmägg, Dlr</t>
+          <t>Blocktjärnen, Blocktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483838</v>
+        <v>483983</v>
       </c>
       <c r="R2" t="n">
-        <v>6836236</v>
+        <v>6836105</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121325391</v>
+        <v>121325458</v>
       </c>
       <c r="B3" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Blocktjärnen, Blocktjärnen, Dlr</t>
+          <t>Vemasmägg, Vemasmägg, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483983</v>
+        <v>483838</v>
       </c>
       <c r="R3" t="n">
-        <v>6836105</v>
+        <v>6836236</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,11 +855,6 @@
           <t>2024-11-24</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På tall</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -872,12 +867,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -887,7 +882,7 @@
         <v>121325384</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -989,7 +984,7 @@
         <v>121325415</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121326083</v>
+        <v>121325391</v>
       </c>
       <c r="B6" t="n">
-        <v>78346</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1134,7 +1129,7 @@
         <v>6836105</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1164,6 +1159,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-24</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 57726-2021 artfynd.xlsx
+++ b/artfynd/A 57726-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121326083</v>
+        <v>121325367</v>
       </c>
       <c r="B2" t="n">
-        <v>78353</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483983</v>
+        <v>483905</v>
       </c>
       <c r="R2" t="n">
-        <v>6836105</v>
+        <v>6836127</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-24</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,19 +777,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121325458</v>
+        <v>121325384</v>
       </c>
       <c r="B3" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -817,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483838</v>
+        <v>483864</v>
       </c>
       <c r="R3" t="n">
-        <v>6836236</v>
+        <v>6836259</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,19 +874,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121325384</v>
+        <v>121325391</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -915,14 +905,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vemasmägg, Vemasmägg, Dlr</t>
+          <t>Blocktjärnen, Blocktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483864</v>
+        <v>483983</v>
       </c>
       <c r="R4" t="n">
-        <v>6836259</v>
+        <v>6836105</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,6 +947,11 @@
           <t>2024-11-24</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På tall</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -969,12 +964,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -984,16 +979,11 @@
         <v>121325415</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1083,19 +1073,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121325391</v>
+        <v>121325458</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1119,14 +1104,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Blocktjärnen, Blocktjärnen, Dlr</t>
+          <t>Vemasmägg, Vemasmägg, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483983</v>
+        <v>483838</v>
       </c>
       <c r="R6" t="n">
-        <v>6836105</v>
+        <v>6836236</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1161,11 +1146,6 @@
           <t>2024-11-24</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På tall</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1178,15 +1158,112 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121326083</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Blocktjärnen, Blocktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>483983</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6836105</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-11-24</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-11-24</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57726-2021 artfynd.xlsx
+++ b/artfynd/A 57726-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121325367</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121325384</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121325391</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121325415</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121325458</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1264,8 +1294,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121326083</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>